--- a/차량_렌탈현황_변경.xlsx
+++ b/차량_렌탈현황_변경.xlsx
@@ -615,7 +615,7 @@
         <is>
           <t>월 기타비용
 (범칙금, 하이패스
-스료 미납)</t>
+이용료 미납)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
